--- a/artfynd/A 15156-2026 artfynd.xlsx
+++ b/artfynd/A 15156-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131933123</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15156-2026 artfynd.xlsx
+++ b/artfynd/A 15156-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131933123</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15156-2026 artfynd.xlsx
+++ b/artfynd/A 15156-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131933123</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15156-2026 artfynd.xlsx
+++ b/artfynd/A 15156-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131933123</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15156-2026 artfynd.xlsx
+++ b/artfynd/A 15156-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131933123</v>
       </c>
       <c r="B2" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
